--- a/设计类清单.xlsx
+++ b/设计类清单.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="21600" windowHeight="9555"/>
+    <workbookView windowWidth="10800" windowHeight="9555"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="28">
   <si>
     <t>序号</t>
   </si>
@@ -36,6 +36,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="仿宋"/>
+        <charset val="134"/>
+      </rPr>
       <t>对应</t>
     </r>
     <r>
@@ -52,7 +58,7 @@
     <t>对应边界类</t>
   </si>
   <si>
-    <t>排班信息</t>
+    <t>排班信息、候诊队列</t>
   </si>
   <si>
     <t>挂号流程控制</t>
@@ -61,31 +67,67 @@
     <t>挂号界面、管理后台界面</t>
   </si>
   <si>
-    <t>药品知识库</t>
-  </si>
-  <si>
-    <t>药品查询控制</t>
-  </si>
-  <si>
-    <t>药品知识库管理界面</t>
-  </si>
-  <si>
-    <t>候诊队列</t>
-  </si>
-  <si>
-    <t>候诊队列管理控制</t>
+    <t>患者挂号记录、候诊队列、科室信息</t>
+  </si>
+  <si>
+    <t>队列查询控制器</t>
+  </si>
+  <si>
+    <t>候诊队列页面、队列信息界面</t>
+  </si>
+  <si>
+    <t>候诊队列、患者挂号信息、科室信息、急诊队列</t>
+  </si>
+  <si>
+    <t>候诊队列管理控制、查询候诊队列</t>
   </si>
   <si>
     <t>候诊队列查询界面、候诊队列管理界面、队列调整结果界面</t>
   </si>
   <si>
-    <t>叫号记录</t>
+    <t>叫号记录、候诊队列</t>
   </si>
   <si>
     <t>叫号控制</t>
   </si>
   <si>
     <t>叫号操作界面、叫号状态界面、当前叫号界面</t>
+  </si>
+  <si>
+    <t>患者排队信息、候诊队列、通知记录</t>
+  </si>
+  <si>
+    <t>过号处理控制器</t>
+  </si>
+  <si>
+    <t>叫号管理界面、过号处理弹窗界面</t>
+  </si>
+  <si>
+    <t>患者就诊记录、药品知识库、用药指导、药房通知</t>
+  </si>
+  <si>
+    <t>用药指导控制器</t>
+  </si>
+  <si>
+    <t>诊断界面、用药指导编辑界面</t>
+  </si>
+  <si>
+    <t>药品知识库、查询日志</t>
+  </si>
+  <si>
+    <t>知识库管理控制、查询请求</t>
+  </si>
+  <si>
+    <t>药品知识库管理界面、查询请求</t>
+  </si>
+  <si>
+    <t>药品知识库、药品信息记录</t>
+  </si>
+  <si>
+    <t>药品库管理控制器</t>
+  </si>
+  <si>
+    <t>药品库管理界面、新增/编辑表单</t>
   </si>
 </sst>
 </file>
@@ -460,16 +502,16 @@
       <diagonal/>
     </border>
     <border>
-      <left style="medium">
+      <left style="thin">
         <color auto="1"/>
       </left>
-      <right style="medium">
+      <right style="thin">
         <color auto="1"/>
       </right>
-      <top style="medium">
+      <top style="thin">
         <color auto="1"/>
       </top>
-      <bottom style="medium">
+      <bottom style="thin">
         <color auto="1"/>
       </bottom>
       <diagonal/>
@@ -722,12 +764,9 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1257,16 +1296,16 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:D5"/>
-  <sheetFormatPr defaultColWidth="9.02654867256637" defaultRowHeight="13.5" outlineLevelRow="4" outlineLevelCol="3"/>
+  <dimension ref="A1:D9"/>
+  <sheetFormatPr defaultColWidth="9.02654867256637" defaultRowHeight="13.5" outlineLevelCol="3"/>
   <cols>
     <col min="1" max="1" width="10.0265486725664" customWidth="1"/>
-    <col min="2" max="2" width="11.1592920353982" customWidth="1"/>
+    <col min="2" max="2" width="21.716814159292" customWidth="1"/>
     <col min="3" max="3" width="16.1327433628319" customWidth="1"/>
     <col min="4" max="4" width="44.212389380531" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="14.25" spans="1:4">
+    <row r="1" spans="1:4">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1284,13 +1323,13 @@
       <c r="A2" s="1">
         <v>1</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="C2" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="D2" s="1" t="s">
         <v>6</v>
       </c>
     </row>
@@ -1298,27 +1337,27 @@
       <c r="A3" s="1">
         <v>2</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B3" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="C3" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="D3" s="1" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="4" ht="31" customHeight="1" spans="1:4">
+    <row r="4" ht="30" customHeight="1" spans="1:4">
       <c r="A4" s="1">
         <v>3</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="B4" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="C4" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="D4" s="2" t="s">
+      <c r="D4" s="1" t="s">
         <v>12</v>
       </c>
     </row>
@@ -1326,14 +1365,70 @@
       <c r="A5" s="1">
         <v>4</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="B5" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="C5" s="2" t="s">
+      <c r="C5" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="D5" s="2" t="s">
+      <c r="D5" s="1" t="s">
         <v>15</v>
+      </c>
+    </row>
+    <row r="6" ht="30" customHeight="1" spans="1:4">
+      <c r="A6" s="1">
+        <v>5</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="7" ht="30" customHeight="1" spans="1:4">
+      <c r="A7" s="1">
+        <v>6</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="8" ht="30" customHeight="1" spans="1:4">
+      <c r="A8" s="1">
+        <v>7</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="9" ht="30" customHeight="1" spans="1:4">
+      <c r="A9" s="1">
+        <v>8</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>27</v>
       </c>
     </row>
   </sheetData>
